--- a/output/yearly_surface_area_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_55_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497647246868</v>
+        <v>10.84497632729258</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907243062002</v>
+        <v>37.78907192475724</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.550400609183966</v>
+        <v>5.127668259281091</v>
       </c>
       <c r="C2" t="n">
-        <v>11.0338624480299</v>
+        <v>11.65825398793087</v>
       </c>
       <c r="D2" t="n">
-        <v>27.80309498426967</v>
+        <v>28.69648539513427</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5445922384165</v>
+        <v>18.14269757448106</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6544501703009</v>
+        <v>21.35792130588936</v>
       </c>
       <c r="D3" t="n">
-        <v>88.06767780946012</v>
+        <v>93.66854846218818</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.35800342134737</v>
+        <v>38.07119422298706</v>
       </c>
       <c r="C4" t="n">
-        <v>85.6889031220701</v>
+        <v>60.50805625584366</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6971012610693</v>
+        <v>108.4448331588069</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.2761995667254</v>
+        <v>46.85390918517903</v>
       </c>
       <c r="C5" t="n">
-        <v>131.4805612912541</v>
+        <v>116.9752389610075</v>
       </c>
       <c r="D5" t="n">
-        <v>75.49639845657973</v>
+        <v>70.93127163183206</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.91705983342032</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="C6" t="n">
-        <v>125.907179574245</v>
+        <v>140.3172723771796</v>
       </c>
       <c r="D6" t="n">
-        <v>50.67683474551611</v>
+        <v>47.17494068446774</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>29.46421209985527</v>
       </c>
       <c r="C7" t="n">
-        <v>107.1371452167502</v>
+        <v>120.3121994077424</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>15.77177686872501</v>
       </c>
       <c r="C8" t="n">
-        <v>71.59886007071988</v>
+        <v>75.60439070404686</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>41.93437143919824</v>
+        <v>40.38124657107979</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.673721145274678</v>
+        <v>7.665962816564958</v>
       </c>
       <c r="C21" t="n">
-        <v>93.04386888645547</v>
+        <v>92.94979915085011</v>
       </c>
       <c r="D21" t="n">
-        <v>7.673721145274678</v>
+        <v>7.665962816564958</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.630323083855457</v>
+        <v>5.965099051003619</v>
       </c>
       <c r="C2" t="n">
-        <v>7.483862749473436</v>
+        <v>8.821984870361838</v>
       </c>
       <c r="D2" t="n">
-        <v>27.5625667967292</v>
+        <v>24.86865109627595</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.77039421039326</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="C3" t="n">
-        <v>34.67532891399734</v>
+        <v>33.04562772494764</v>
       </c>
       <c r="D3" t="n">
-        <v>89.07396920631311</v>
+        <v>93.89925917268619</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.49464627868692</v>
+        <v>35.85048091598077</v>
       </c>
       <c r="C4" t="n">
-        <v>76.19343932659496</v>
+        <v>56.3729349255561</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9778243512217</v>
+        <v>124.8449285582499</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.09872421643498</v>
+        <v>51.14905539125883</v>
       </c>
       <c r="C5" t="n">
-        <v>142.5006792714246</v>
+        <v>113.1218792218388</v>
       </c>
       <c r="D5" t="n">
-        <v>91.49888603580274</v>
+        <v>89.90354601640168</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.24286120251001</v>
+        <v>51.24035792775378</v>
       </c>
       <c r="C6" t="n">
-        <v>164.3072592781547</v>
+        <v>161.690901646337</v>
       </c>
       <c r="D6" t="n">
-        <v>61.22276858453534</v>
+        <v>56.03030497677397</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.6743471662931</v>
+        <v>38.86640986342697</v>
       </c>
       <c r="C7" t="n">
-        <v>140.6137601838622</v>
+        <v>157.2023511425205</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.69385894719101</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="C8" t="n">
-        <v>104.2272450213626</v>
+        <v>114.3245201595411</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>62.90155715879737</v>
+        <v>64.12186955517615</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.848820795510853</v>
+        <v>7.839822109063184</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0535677422022</v>
+        <v>100.9377096541885</v>
       </c>
       <c r="D21" t="n">
-        <v>8.829923394949709</v>
+        <v>8.819799872696082</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.527640485537042</v>
+        <v>7.954119899807657</v>
       </c>
       <c r="C2" t="n">
-        <v>15.79337531821844</v>
+        <v>14.11065975313941</v>
       </c>
       <c r="D2" t="n">
-        <v>25.76007801173206</v>
+        <v>26.47577208812798</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25774198232718</v>
+        <v>18.2065111752571</v>
       </c>
       <c r="C3" t="n">
-        <v>31.80862561759665</v>
+        <v>33.29106465100934</v>
       </c>
       <c r="D3" t="n">
-        <v>89.22123136195013</v>
+        <v>91.5381559439726</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.18008610270045</v>
+        <v>33.85949657176824</v>
       </c>
       <c r="C4" t="n">
-        <v>79.76700097005333</v>
+        <v>67.13190801639689</v>
       </c>
       <c r="D4" t="n">
-        <v>132.0558654459427</v>
+        <v>137.0205635863188</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.27053006467818</v>
+        <v>52.327152636355</v>
       </c>
       <c r="C5" t="n">
-        <v>139.825416777352</v>
+        <v>107.7222668484813</v>
       </c>
       <c r="D5" t="n">
-        <v>109.0230825566083</v>
+        <v>108.7776456305466</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.83784136901259</v>
+        <v>58.04288777047993</v>
       </c>
       <c r="C6" t="n">
-        <v>190.8331004991993</v>
+        <v>169.8619877887832</v>
       </c>
       <c r="D6" t="n">
-        <v>71.72845076768047</v>
+        <v>67.01900703040852</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.27994663109313</v>
+        <v>47.60985491744906</v>
       </c>
       <c r="C7" t="n">
-        <v>179.8394897070435</v>
+        <v>188.2236151013112</v>
       </c>
       <c r="D7" t="n">
-        <v>50.2448657556475</v>
+        <v>47.9691745772034</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C8" t="n">
-        <v>138.190806849781</v>
+        <v>153.1280981698962</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>15.97499864350409</v>
       </c>
       <c r="C9" t="n">
-        <v>90.96874227550941</v>
+        <v>96.73749178566366</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>53.38253141842032</v>
       </c>
       <c r="D10" t="n">
         <v>35.73070769606267</v>
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>37.84931924182727</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.00777467061601</v>
+        <v>7.998464303969956</v>
       </c>
       <c r="C21" t="n">
-        <v>108.1049580533161</v>
+        <v>107.9792681035944</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00971833827001</v>
+        <v>9.998080379962445</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.976880023454582</v>
+        <v>7.208973392284329</v>
       </c>
       <c r="C2" t="n">
-        <v>10.86500184289945</v>
+        <v>9.707521299592461</v>
       </c>
       <c r="D2" t="n">
-        <v>21.46395005794801</v>
+        <v>22.05888916672158</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3453385121834</v>
+        <v>22.41820882647592</v>
       </c>
       <c r="C3" t="n">
-        <v>52.33697011339746</v>
+        <v>50.76617378660256</v>
       </c>
       <c r="D3" t="n">
-        <v>96.9721294869787</v>
+        <v>99.67193567365743</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.7904711328347</v>
+        <v>25.12979598560561</v>
       </c>
       <c r="C4" t="n">
-        <v>112.6820562503362</v>
+        <v>89.86231261282329</v>
       </c>
       <c r="D4" t="n">
-        <v>125.3809628047687</v>
+        <v>128.5333546831052</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.6424892714007</v>
+        <v>32.69219855141879</v>
       </c>
       <c r="C5" t="n">
-        <v>114.029995848267</v>
+        <v>101.488168926514</v>
       </c>
       <c r="D5" t="n">
-        <v>72.15845626214058</v>
+        <v>69.28684422721865</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.24407962992574</v>
+        <v>29.54471541160352</v>
       </c>
       <c r="C6" t="n">
-        <v>118.4203715816588</v>
+        <v>123.9751000922872</v>
       </c>
       <c r="D6" t="n">
-        <v>33.08686112852601</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>97.13608135358791</v>
+        <v>107.6761247063817</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>27.84727363096077</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>67.00918955336604</v>
+        <v>71.26506585127596</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.43141351498762</v>
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.724750789912399</v>
+        <v>4.420809912223387</v>
       </c>
       <c r="C2" t="n">
-        <v>5.727516106575892</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="D2" t="n">
-        <v>15.77864910265474</v>
+        <v>15.35158885130737</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36635612460008</v>
+        <v>24.04300127700439</v>
       </c>
       <c r="C3" t="n">
-        <v>48.35598317267664</v>
+        <v>45.24384295021426</v>
       </c>
       <c r="D3" t="n">
-        <v>93.72254458592175</v>
+        <v>96.32908474069704</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.59300097556086</v>
+        <v>32.65980087717864</v>
       </c>
       <c r="C4" t="n">
-        <v>124.1302162295582</v>
+        <v>109.5807152526205</v>
       </c>
       <c r="D4" t="n">
-        <v>141.0152949948991</v>
+        <v>144.6654329592888</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.19503330244241</v>
+        <v>36.1528592088888</v>
       </c>
       <c r="C5" t="n">
-        <v>158.5031668506475</v>
+        <v>133.0022702328367</v>
       </c>
       <c r="D5" t="n">
-        <v>93.11876974780998</v>
+        <v>91.37616757277189</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.19503330244241</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="C6" t="n">
-        <v>147.522318778647</v>
+        <v>144.5839478998363</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>126.5404068434841</v>
+        <v>137.4397698560322</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.30262463928205</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>87.2871883845839</v>
+        <v>94.29686699290613</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.746349239405828</v>
+        <v>4.922482989093507</v>
       </c>
       <c r="C2" t="n">
-        <v>5.109996800604648</v>
+        <v>7.340527584653401</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0239471599962</v>
+        <v>27.43101260436013</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66516727958961</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="C3" t="n">
-        <v>34.89131340893164</v>
+        <v>31.29811681138832</v>
       </c>
       <c r="D3" t="n">
-        <v>85.40714153095126</v>
+        <v>87.19392235268047</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.62151271671301</v>
+        <v>39.07944911524854</v>
       </c>
       <c r="C4" t="n">
-        <v>122.3051472473634</v>
+        <v>111.1632925518663</v>
       </c>
       <c r="D4" t="n">
-        <v>153.4717098663826</v>
+        <v>157.530254875739</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.9074222828271</v>
+        <v>42.04334543436966</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6742783552896</v>
+        <v>166.0380804807418</v>
       </c>
       <c r="D5" t="n">
-        <v>117.6379186613741</v>
+        <v>117.2943069648877</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>41.29819892684633</v>
       </c>
       <c r="C6" t="n">
-        <v>194.6972594631147</v>
+        <v>177.0670341902505</v>
       </c>
       <c r="D6" t="n">
-        <v>56.55357650313753</v>
+        <v>54.58124536530568</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="C7" t="n">
-        <v>166.8440953459284</v>
+        <v>171.4553643127757</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>123.0031698650829</v>
+        <v>133.2673421129833</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>71.88749389576842</v>
+        <v>74.43905617910588</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.70955121492574</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.235439522569987</v>
+        <v>2.943279617331937</v>
       </c>
       <c r="C2" t="n">
-        <v>2.45927799913826</v>
+        <v>3.500912313344126</v>
       </c>
       <c r="D2" t="n">
-        <v>16.09575361112646</v>
+        <v>19.15487945755952</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.68971097219578</v>
+        <v>20.14055415262332</v>
       </c>
       <c r="C3" t="n">
-        <v>30.82196917482861</v>
+        <v>32.16696352964674</v>
       </c>
       <c r="D3" t="n">
-        <v>86.58033003752621</v>
+        <v>90.43368977669495</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.83771819582557</v>
+        <v>42.71682435948296</v>
       </c>
       <c r="C4" t="n">
-        <v>122.6625034117092</v>
+        <v>110.0784613386736</v>
       </c>
       <c r="D4" t="n">
-        <v>162.673631098288</v>
+        <v>166.8598033091964</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.79728661350221</v>
+        <v>43.93320976504477</v>
       </c>
       <c r="C5" t="n">
-        <v>231.790632972672</v>
+        <v>203.5162990903638</v>
       </c>
       <c r="D5" t="n">
-        <v>124.0192787389783</v>
+        <v>123.7738418129166</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.66547037922588</v>
+        <v>33.81139093426016</v>
       </c>
       <c r="C6" t="n">
-        <v>226.9790874741583</v>
+        <v>210.1941469746506</v>
       </c>
       <c r="D6" t="n">
-        <v>55.06426523579511</v>
+        <v>53.13218575383738</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>168.4610338148229</v>
+        <v>176.4858395493364</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>89.12305659152544</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.321833320543707</v>
+        <v>3.097414006898687</v>
       </c>
       <c r="C2" t="n">
-        <v>5.827654372409066</v>
+        <v>5.142394474844792</v>
       </c>
       <c r="D2" t="n">
-        <v>20.76003695400305</v>
+        <v>14.7900291644782</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.38965602759475</v>
+        <v>15.34471661737765</v>
       </c>
       <c r="C3" t="n">
-        <v>20.20436775339936</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D3" t="n">
-        <v>80.11552140506097</v>
+        <v>85.18133955897451</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.19132729580366</v>
+        <v>40.59821281371835</v>
       </c>
       <c r="C4" t="n">
-        <v>101.6805914765464</v>
+        <v>96.65207973539424</v>
       </c>
       <c r="D4" t="n">
-        <v>167.3064985146287</v>
+        <v>172.2711966550048</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.39953992456201</v>
+        <v>52.4989584845982</v>
       </c>
       <c r="C5" t="n">
-        <v>230.9561474240622</v>
+        <v>204.7434837206723</v>
       </c>
       <c r="D5" t="n">
-        <v>147.4339614852648</v>
+        <v>148.3911654969054</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>43.75354993516761</v>
       </c>
       <c r="C6" t="n">
-        <v>288.9263858644279</v>
+        <v>260.2269552261808</v>
       </c>
       <c r="D6" t="n">
-        <v>74.78757661411353</v>
+        <v>73.09700706740053</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>236.3724495083918</v>
+        <v>230.2041286826091</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>140.7777120504714</v>
+        <v>149.3729132011522</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>59.01874498850123</v>
+        <v>61.4593697812588</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.624792450528471</v>
+        <v>2.116648050356123</v>
       </c>
       <c r="C2" t="n">
-        <v>3.477350368442202</v>
+        <v>2.938370878810703</v>
       </c>
       <c r="D2" t="n">
-        <v>14.75566799482956</v>
+        <v>10.78548027885546</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.65196259107789</v>
+        <v>13.49412219487241</v>
       </c>
       <c r="C3" t="n">
-        <v>21.65735435568464</v>
+        <v>21.82425146540659</v>
       </c>
       <c r="D3" t="n">
-        <v>78.53490760122361</v>
+        <v>79.42338927356695</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.96235909653591</v>
+        <v>37.17780381212246</v>
       </c>
       <c r="C4" t="n">
-        <v>82.63861300497526</v>
+        <v>82.8300538073034</v>
       </c>
       <c r="D4" t="n">
-        <v>168.9401266944954</v>
+        <v>174.8237406860465</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.25289966373074</v>
+        <v>56.64684253504097</v>
       </c>
       <c r="C5" t="n">
-        <v>222.7585540936013</v>
+        <v>201.8227843005381</v>
       </c>
       <c r="D5" t="n">
-        <v>164.1727598426729</v>
+        <v>166.0380804807418</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.86801350593698</v>
+        <v>50.99884799250906</v>
       </c>
       <c r="C6" t="n">
-        <v>327.0849556330929</v>
+        <v>293.032054763588</v>
       </c>
       <c r="D6" t="n">
-        <v>88.19137802019524</v>
+        <v>86.74231840872694</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.61233283000952</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>296.07939963757</v>
+        <v>279.0117157992393</v>
       </c>
       <c r="D7" t="n">
-        <v>44.85507085933252</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>181.58405537749</v>
+        <v>191.8482276253905</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>67.67186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.386628669023996</v>
+        <v>4.247040568571702</v>
       </c>
       <c r="C2" t="n">
-        <v>7.523132657643308</v>
+        <v>9.072330534944774</v>
       </c>
       <c r="D2" t="n">
-        <v>15.77668560724624</v>
+        <v>15.23279737909351</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.261406931236911</v>
+        <v>10.51942665100457</v>
       </c>
       <c r="C3" t="n">
-        <v>18.03961406553514</v>
+        <v>16.99405276051229</v>
       </c>
       <c r="D3" t="n">
-        <v>73.1009340582175</v>
+        <v>72.04064653763095</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.95937279569416</v>
+        <v>31.9961394291078</v>
       </c>
       <c r="C4" t="n">
-        <v>70.29706261488862</v>
+        <v>70.33535077535424</v>
       </c>
       <c r="D4" t="n">
-        <v>166.9108541898172</v>
+        <v>172.0797558526767</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.44295780772712</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6006472774711</v>
+        <v>180.8624708148687</v>
       </c>
       <c r="D5" t="n">
-        <v>180.764296044444</v>
+        <v>183.8568013128214</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.83784136901259</v>
+        <v>60.13597387593413</v>
       </c>
       <c r="C6" t="n">
-        <v>338.3956709337204</v>
+        <v>304.825789934705</v>
       </c>
       <c r="D6" t="n">
-        <v>109.6455106011008</v>
+        <v>108.7599741718702</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>363.1524027917121</v>
+        <v>335.7842220404238</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>53.23919625360028</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>258.4401744044516</v>
+        <v>261.1939767148639</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>120.9218647320796</v>
+        <v>127.0234267139735</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.529783907394783</v>
+        <v>6.503096792930871</v>
       </c>
       <c r="C2" t="n">
-        <v>8.080765353655496</v>
+        <v>6.180101798233672</v>
       </c>
       <c r="D2" t="n">
-        <v>15.80908328148639</v>
+        <v>7.906996010003811</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.743583922742335</v>
+        <v>3.067961575771282</v>
       </c>
       <c r="C2" t="n">
-        <v>4.393320976504477</v>
+        <v>5.297510612115789</v>
       </c>
       <c r="D2" t="n">
-        <v>11.73777555197486</v>
+        <v>11.33231375012093</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.21155878249857</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="C3" t="n">
-        <v>24.14117604742907</v>
+        <v>24.64186737659494</v>
       </c>
       <c r="D3" t="n">
-        <v>79.52156404399165</v>
+        <v>77.86731916233578</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.05468443846411</v>
+        <v>43.04865508351838</v>
       </c>
       <c r="C4" t="n">
-        <v>103.7098639812246</v>
+        <v>102.025184920737</v>
       </c>
       <c r="D4" t="n">
-        <v>169.9739070270673</v>
+        <v>176.5722333473101</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.05973204570559</v>
+        <v>34.90113088597411</v>
       </c>
       <c r="C5" t="n">
-        <v>288.4620192003191</v>
+        <v>262.1266370338984</v>
       </c>
       <c r="D5" t="n">
-        <v>163.5591675275186</v>
+        <v>165.4981192434061</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.22141731727005</v>
+        <v>18.95852991671016</v>
       </c>
       <c r="C6" t="n">
-        <v>298.8685448653353</v>
+        <v>277.8974321549192</v>
       </c>
       <c r="D6" t="n">
-        <v>83.84419918579036</v>
+        <v>82.71715282131501</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>181.7558612257332</v>
+        <v>183.672232744423</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>32.45854259780804</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>89.12305659152544</v>
+        <v>93.6292785540183</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.267477343911637</v>
+        <v>6.650358948567893</v>
       </c>
       <c r="C2" t="n">
-        <v>4.540583132141498</v>
+        <v>8.546113765468485</v>
       </c>
       <c r="D2" t="n">
-        <v>22.44667950989907</v>
+        <v>19.8695917862512</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.626036240139976</v>
+        <v>13.81319019875262</v>
       </c>
       <c r="C3" t="n">
-        <v>20.36144738607885</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41482161500667</v>
+        <v>9.778207134298231</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39712405952618</v>
+        <v>13.39846735566139</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13788478222529</v>
+        <v>70.14491733258021</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576132242297197</v>
+        <v>1.576290277136634</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.637776154861932</v>
+        <v>4.833143948007048</v>
       </c>
       <c r="C2" t="n">
-        <v>5.05698242457532</v>
+        <v>7.247261552749954</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79497896072844</v>
+        <v>23.96249796525615</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.80261195818416</v>
+        <v>19.3306122966197</v>
       </c>
       <c r="C3" t="n">
-        <v>18.70229376590174</v>
+        <v>26.67899386290707</v>
       </c>
       <c r="D3" t="n">
-        <v>31.30302554990955</v>
+        <v>24.1019061392592</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.30777005751476</v>
+        <v>16.04273923509713</v>
       </c>
       <c r="C4" t="n">
-        <v>31.58773238414112</v>
+        <v>24.27469373520663</v>
       </c>
       <c r="D4" t="n">
-        <v>23.67484588791183</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43810767559577</v>
+        <v>15.44061361929703</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12839019016587</v>
+        <v>86.14237071818346</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250127931704372</v>
+        <v>3.250655498799376</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.511130701014094</v>
+        <v>4.5553093477052</v>
       </c>
       <c r="C2" t="n">
-        <v>8.821984870361838</v>
+        <v>7.272786993060371</v>
       </c>
       <c r="D2" t="n">
-        <v>18.35770032171111</v>
+        <v>20.21123998732908</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3902779224005</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>19.29134238844982</v>
+        <v>27.60183670489907</v>
       </c>
       <c r="D3" t="n">
-        <v>39.87368300798421</v>
+        <v>37.67947688899258</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.34301516387641</v>
+        <v>28.21837426316607</v>
       </c>
       <c r="C4" t="n">
-        <v>40.57268737340794</v>
+        <v>49.30238795957057</v>
       </c>
       <c r="D4" t="n">
-        <v>34.02541193378595</v>
+        <v>27.72062817711294</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.234719816773</v>
+        <v>13.8671863224862</v>
       </c>
       <c r="C5" t="n">
-        <v>35.61289797155305</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="D5" t="n">
-        <v>31.14594591723007</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
         <v>30.91916219754903</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.23368131580652</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73009315866688</v>
+        <v>16.73185862203844</v>
       </c>
       <c r="C21" t="n">
-        <v>102.053568267868</v>
+        <v>102.0643375944345</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182523289666721</v>
+        <v>4.182964655509609</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.358378969779091</v>
+        <v>6.404922022506191</v>
       </c>
       <c r="C2" t="n">
-        <v>8.437139770297089</v>
+        <v>8.647233779005905</v>
       </c>
       <c r="D2" t="n">
-        <v>25.3771964070758</v>
+        <v>34.87953243648068</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.87976911619216</v>
+        <v>16.78297700409922</v>
       </c>
       <c r="C3" t="n">
-        <v>27.90617849321558</v>
+        <v>27.94544840138546</v>
       </c>
       <c r="D3" t="n">
-        <v>44.95422737746145</v>
+        <v>44.6597030661874</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.00140802052752</v>
+        <v>31.42181702212341</v>
       </c>
       <c r="C4" t="n">
-        <v>44.8737240657132</v>
+        <v>60.34214089382595</v>
       </c>
       <c r="D4" t="n">
-        <v>45.69053815564656</v>
+        <v>39.67929696254333</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.50656611985813</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="C5" t="n">
-        <v>56.49958037940395</v>
+        <v>61.97282383057992</v>
       </c>
       <c r="D5" t="n">
-        <v>35.80924751240241</v>
+        <v>32.7658296292373</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.982410656781569</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>35.58246379272141</v>
+        <v>28.6591789823729</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05495745786504</v>
+        <v>18.05458821985563</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7871034155957</v>
+        <v>117.7846945771534</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018319152621678</v>
+        <v>6.018196073285211</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.585162689460105</v>
+        <v>7.119634351197869</v>
       </c>
       <c r="C2" t="n">
-        <v>12.56342537124643</v>
+        <v>7.527059648460295</v>
       </c>
       <c r="D2" t="n">
-        <v>37.91804158112456</v>
+        <v>35.90644053512284</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37416904850505</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>28.83883881225006</v>
+        <v>29.18735924725767</v>
       </c>
       <c r="D3" t="n">
-        <v>51.03124566674921</v>
+        <v>57.60404654668159</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.36479353981909</v>
+        <v>23.3302524437212</v>
       </c>
       <c r="C4" t="n">
-        <v>49.25133707894974</v>
+        <v>54.36918786118836</v>
       </c>
       <c r="D4" t="n">
-        <v>49.95328668748621</v>
+        <v>45.72882631611218</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.92947839621025</v>
+        <v>22.89926520155685</v>
       </c>
       <c r="C5" t="n">
-        <v>52.10625940289948</v>
+        <v>65.75255249193013</v>
       </c>
       <c r="D5" t="n">
-        <v>35.12202411942965</v>
+        <v>31.56318869153496</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.98870205363455</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="C6" t="n">
         <v>43.35103337642641</v>
       </c>
       <c r="D6" t="n">
-        <v>31.91956310817655</v>
+        <v>30.95352336719769</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>23.29589127407256</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="D7" t="n">
         <v>30.78171751895449</v>
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056024805083355</v>
+        <v>7.053735774941468</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15023254765646</v>
+        <v>66.12877289007626</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410015503177097</v>
+        <v>4.408584859338418</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.571999058677396</v>
+        <v>5.62050560681299</v>
       </c>
       <c r="C2" t="n">
-        <v>7.488771487994669</v>
+        <v>3.878885179479147</v>
       </c>
       <c r="D2" t="n">
-        <v>33.59933343014283</v>
+        <v>39.73231133857266</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.90216938694059</v>
+        <v>21.97642235956485</v>
       </c>
       <c r="C3" t="n">
-        <v>41.90099201725387</v>
+        <v>29.31007771028852</v>
       </c>
       <c r="D3" t="n">
-        <v>70.54839002717578</v>
+        <v>73.84706231344508</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.623034243765</v>
+        <v>30.12001956629214</v>
       </c>
       <c r="C4" t="n">
-        <v>63.78807533573226</v>
+        <v>65.52380527684062</v>
       </c>
       <c r="D4" t="n">
-        <v>64.63041486597602</v>
+        <v>65.30683903420207</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.243498792849</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="C5" t="n">
-        <v>75.96272861609697</v>
+        <v>87.10556505929826</v>
       </c>
       <c r="D5" t="n">
-        <v>46.33849164044945</v>
+        <v>41.11068511533519</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.16607959293373</v>
+        <v>23.70822530985623</v>
       </c>
       <c r="C6" t="n">
-        <v>66.65674212754145</v>
+        <v>79.33601372788901</v>
       </c>
       <c r="D6" t="n">
-        <v>36.38749691020379</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>46.29234949834984</v>
+        <v>44.91495746929157</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>25.95250056176443</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>21.07321447165778</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27632666755051</v>
+        <v>7.27236205945343</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49188917583655</v>
+        <v>75.45075636682934</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457245000662883</v>
+        <v>5.454271544590072</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.653083207502381</v>
+        <v>4.744786654624835</v>
       </c>
       <c r="C2" t="n">
-        <v>5.281802648847839</v>
+        <v>5.64504929941916</v>
       </c>
       <c r="D2" t="n">
-        <v>33.69947169597602</v>
+        <v>32.56751659297944</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.70934592628072</v>
+        <v>20.52343575727957</v>
       </c>
       <c r="C3" t="n">
-        <v>34.26790361673491</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D3" t="n">
-        <v>81.0579992011379</v>
+        <v>89.20650514638643</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.05169813762236</v>
+        <v>37.21609197258809</v>
       </c>
       <c r="C4" t="n">
-        <v>87.60331114535138</v>
+        <v>70.10562181256049</v>
       </c>
       <c r="D4" t="n">
-        <v>85.47193687943155</v>
+        <v>85.80376760346698</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.3366259560322</v>
+        <v>37.87091769132071</v>
       </c>
       <c r="C5" t="n">
-        <v>98.73927535462298</v>
+        <v>106.2005579068987</v>
       </c>
       <c r="D5" t="n">
-        <v>59.12575548826417</v>
+        <v>55.24785205648926</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.98119222936585</v>
+        <v>32.8453511932813</v>
       </c>
       <c r="C6" t="n">
-        <v>96.44296747438969</v>
+        <v>111.3360801478138</v>
       </c>
       <c r="D6" t="n">
-        <v>42.34474197957343</v>
+        <v>39.36611944488861</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>73.72041685959724</v>
+        <v>81.68533598415159</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>45.14566817978957</v>
+        <v>43.14290286312608</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>18.82992096745382</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.482706671352195</v>
+        <v>7.476552695977202</v>
       </c>
       <c r="C21" t="n">
-        <v>84.1804500527122</v>
+        <v>84.11121782974352</v>
       </c>
       <c r="D21" t="n">
-        <v>6.547368337433171</v>
+        <v>6.541983608980051</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_55_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497632729258</v>
+        <v>10.84497622413629</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907192475724</v>
+        <v>37.7890715653115</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.127668259281091</v>
+        <v>6.201700247727102</v>
       </c>
       <c r="C2" t="n">
-        <v>11.65825398793087</v>
+        <v>10.18465068385641</v>
       </c>
       <c r="D2" t="n">
-        <v>28.69648539513427</v>
+        <v>38.17231423652448</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14269757448106</v>
+        <v>20.80323385298991</v>
       </c>
       <c r="C3" t="n">
-        <v>21.35792130588936</v>
+        <v>34.44461820349934</v>
       </c>
       <c r="D3" t="n">
-        <v>93.66854846218818</v>
+        <v>99.17124434449156</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.07119422298706</v>
+        <v>41.98934931063608</v>
       </c>
       <c r="C4" t="n">
-        <v>60.50805625584366</v>
+        <v>70.08009637225007</v>
       </c>
       <c r="D4" t="n">
-        <v>108.4448331588069</v>
+        <v>106.7601540983194</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.85390918517903</v>
+        <v>49.75006491270713</v>
       </c>
       <c r="C5" t="n">
-        <v>116.9752389610075</v>
+        <v>89.09360416039806</v>
       </c>
       <c r="D5" t="n">
-        <v>70.93127163183206</v>
+        <v>69.43410638285567</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>45.00135126726531</v>
       </c>
       <c r="C6" t="n">
-        <v>140.3172723771796</v>
+        <v>107.3109145604019</v>
       </c>
       <c r="D6" t="n">
-        <v>47.17494068446774</v>
+        <v>44.92084795551706</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>33.53650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>120.3121994077424</v>
+        <v>92.88413204649498</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.77177686872501</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="C8" t="n">
-        <v>75.60439070404686</v>
+        <v>59.41537106101696</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
         <v>35.01894061048373</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.665962816564958</v>
+        <v>7.689536051041334</v>
       </c>
       <c r="C21" t="n">
-        <v>92.94979915085011</v>
+        <v>94.19681662525633</v>
       </c>
       <c r="D21" t="n">
-        <v>7.665962816564958</v>
+        <v>8.650728057421501</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.965099051003619</v>
+        <v>7.637015391335938</v>
       </c>
       <c r="C2" t="n">
-        <v>8.821984870361838</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86865109627595</v>
+        <v>35.48134377918397</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47510913559323</v>
+        <v>20.62651926622549</v>
       </c>
       <c r="C3" t="n">
-        <v>33.04562772494764</v>
+        <v>36.82535638629786</v>
       </c>
       <c r="D3" t="n">
-        <v>93.89925917268619</v>
+        <v>104.9733732765902</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.85048091598077</v>
+        <v>40.35572113076939</v>
       </c>
       <c r="C4" t="n">
-        <v>56.3729349255561</v>
+        <v>77.09959245761476</v>
       </c>
       <c r="D4" t="n">
-        <v>124.8449285582499</v>
+        <v>128.1632357986041</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.14905539125883</v>
+        <v>55.54237636776331</v>
       </c>
       <c r="C5" t="n">
-        <v>113.1218792218388</v>
+        <v>108.2867717784232</v>
       </c>
       <c r="D5" t="n">
-        <v>89.90354601640168</v>
+        <v>87.52280783360315</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.24035792775378</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="C6" t="n">
-        <v>161.690901646337</v>
+        <v>122.3247822014483</v>
       </c>
       <c r="D6" t="n">
-        <v>56.03030497677397</v>
+        <v>54.90325861229863</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.86640986342697</v>
+        <v>42.69915290080652</v>
       </c>
       <c r="C7" t="n">
-        <v>157.2023511425205</v>
+        <v>121.3302717770463</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.86490403190821</v>
+        <v>26.20284622634736</v>
       </c>
       <c r="C8" t="n">
-        <v>114.3245201595411</v>
+        <v>89.54029936583034</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>12.7578114166873</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>52.58437053486764</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.839822109063184</v>
+        <v>7.867954333563616</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9377096541885</v>
+        <v>102.283406336327</v>
       </c>
       <c r="D21" t="n">
-        <v>8.819799872696082</v>
+        <v>9.834942916954519</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.954119899807657</v>
+        <v>9.690831588620265</v>
       </c>
       <c r="C2" t="n">
-        <v>14.11065975313941</v>
+        <v>9.619164006210248</v>
       </c>
       <c r="D2" t="n">
-        <v>26.47577208812798</v>
+        <v>33.00243082596078</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2065111752571</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="C3" t="n">
-        <v>33.29106465100934</v>
+        <v>44.65479432766617</v>
       </c>
       <c r="D3" t="n">
-        <v>91.5381559439726</v>
+        <v>106.9466861621263</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.85949657176824</v>
+        <v>38.90077103307561</v>
       </c>
       <c r="C4" t="n">
-        <v>67.13190801639689</v>
+        <v>83.54476613599506</v>
       </c>
       <c r="D4" t="n">
-        <v>137.0205635863188</v>
+        <v>143.8741443096658</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.327152636355</v>
+        <v>57.16226007977055</v>
       </c>
       <c r="C5" t="n">
-        <v>107.7222668484813</v>
+        <v>121.4912784005428</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7776456305466</v>
+        <v>107.7468105410875</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.04288777047993</v>
+        <v>63.35610634586367</v>
       </c>
       <c r="C6" t="n">
-        <v>169.8619877887832</v>
+        <v>142.3298551708856</v>
       </c>
       <c r="D6" t="n">
-        <v>67.01900703040852</v>
+        <v>65.52969576306612</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.60985491744906</v>
+        <v>52.4007837141735</v>
       </c>
       <c r="C7" t="n">
-        <v>188.2236151013112</v>
+        <v>145.6442354204228</v>
       </c>
       <c r="D7" t="n">
-        <v>47.9691745772034</v>
+        <v>46.95110220789945</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.54217107911827</v>
+        <v>34.79804737702819</v>
       </c>
       <c r="C8" t="n">
-        <v>153.1280981698962</v>
+        <v>118.9976392317559</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97499864350409</v>
+        <v>18.19374845510188</v>
       </c>
       <c r="C9" t="n">
-        <v>96.73749178566366</v>
+        <v>76.76874348128355</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>53.38253141842032</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.998464303969956</v>
+        <v>8.029580542055871</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9792681035944</v>
+        <v>110.4067324532682</v>
       </c>
       <c r="D21" t="n">
-        <v>9.998080379962445</v>
+        <v>11.04067324532682</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.208973392284329</v>
+        <v>8.754244278768809</v>
       </c>
       <c r="C2" t="n">
-        <v>9.707521299592461</v>
+        <v>6.617961274327748</v>
       </c>
       <c r="D2" t="n">
-        <v>22.05888916672158</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.41820882647592</v>
+        <v>26.85079971115026</v>
       </c>
       <c r="C3" t="n">
-        <v>50.76617378660256</v>
+        <v>61.51631114810514</v>
       </c>
       <c r="D3" t="n">
-        <v>99.67193567365743</v>
+        <v>114.5306871774329</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.12979598560561</v>
+        <v>27.45261105385356</v>
       </c>
       <c r="C4" t="n">
-        <v>89.86231261282329</v>
+        <v>106.3517470533527</v>
       </c>
       <c r="D4" t="n">
-        <v>128.5333546831052</v>
+        <v>132.6429505730823</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.69219855141879</v>
+        <v>35.68652904937156</v>
       </c>
       <c r="C5" t="n">
-        <v>101.488168926514</v>
+        <v>85.04389488037997</v>
       </c>
       <c r="D5" t="n">
-        <v>69.28684422721865</v>
+        <v>68.10874698212248</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.54471541160352</v>
+        <v>32.52333794628834</v>
       </c>
       <c r="C6" t="n">
-        <v>123.9751000922872</v>
+        <v>95.91969594802613</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>30.91327171132357</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>107.6761247063817</v>
+        <v>83.66159411280043</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>71.26506585127596</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.420809912223387</v>
+        <v>5.271003424101125</v>
       </c>
       <c r="C2" t="n">
-        <v>4.697662764820988</v>
+        <v>3.1857713002809</v>
       </c>
       <c r="D2" t="n">
-        <v>15.35158885130737</v>
+        <v>19.38657191576177</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.04300127700439</v>
+        <v>29.1039106923967</v>
       </c>
       <c r="C3" t="n">
-        <v>45.24384295021426</v>
+        <v>44.20809912223388</v>
       </c>
       <c r="D3" t="n">
-        <v>96.32908474069704</v>
+        <v>112.1057703479433</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.65980087717864</v>
+        <v>37.99461790205581</v>
       </c>
       <c r="C4" t="n">
-        <v>109.5807152526205</v>
+        <v>132.9109676963417</v>
       </c>
       <c r="D4" t="n">
-        <v>144.6654329592888</v>
+        <v>153.6631506687108</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.1528592088888</v>
+        <v>39.46625771072178</v>
       </c>
       <c r="C5" t="n">
-        <v>133.0022702328367</v>
+        <v>135.5302705712722</v>
       </c>
       <c r="D5" t="n">
-        <v>91.37616757277189</v>
+        <v>90.66440048719295</v>
       </c>
     </row>
     <row r="6">
@@ -2080,10 +2080,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.22019888985433</v>
+        <v>38.76234460677682</v>
       </c>
       <c r="C6" t="n">
-        <v>144.5839478998363</v>
+        <v>115.4820007028481</v>
       </c>
       <c r="D6" t="n">
         <v>39.16486116551801</v>
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="C7" t="n">
-        <v>137.4397698560322</v>
+        <v>106.5981657271187</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>94.29686699290613</v>
+        <v>74.10231671654924</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>44.92968368485526</v>
+        <v>40.49218406165969</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.922482989093507</v>
+        <v>4.719261214314417</v>
       </c>
       <c r="C2" t="n">
-        <v>7.340527584653401</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="D2" t="n">
-        <v>27.43101260436013</v>
+        <v>18.07495698288803</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.51223562190536</v>
+        <v>23.4834050855837</v>
       </c>
       <c r="C3" t="n">
-        <v>31.29811681138832</v>
+        <v>27.71473769088746</v>
       </c>
       <c r="D3" t="n">
-        <v>87.19392235268047</v>
+        <v>102.5042778004095</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.07944911524854</v>
+        <v>46.49458952542469</v>
       </c>
       <c r="C4" t="n">
-        <v>111.1632925518663</v>
+        <v>121.5138585977405</v>
       </c>
       <c r="D4" t="n">
-        <v>157.530254875739</v>
+        <v>171.4799080053819</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.04334543436966</v>
+        <v>47.34478303730243</v>
       </c>
       <c r="C5" t="n">
-        <v>166.0380804807418</v>
+        <v>188.0292290558704</v>
       </c>
       <c r="D5" t="n">
-        <v>117.2943069648877</v>
+        <v>119.355977143806</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.29819892684633</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="C6" t="n">
-        <v>177.0670341902505</v>
+        <v>162.6569413873158</v>
       </c>
       <c r="D6" t="n">
-        <v>54.58124536530568</v>
+        <v>54.37998708593508</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.02693346083794</v>
+        <v>31.38058361854505</v>
       </c>
       <c r="C7" t="n">
-        <v>171.4553643127757</v>
+        <v>135.04430545767</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>133.2673421129833</v>
+        <v>103.9768993567797</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>74.43905617910588</v>
+        <v>61.90311974357836</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.943279617331937</v>
+        <v>2.852958828541231</v>
       </c>
       <c r="C2" t="n">
-        <v>3.500912313344126</v>
+        <v>3.704134088123216</v>
       </c>
       <c r="D2" t="n">
-        <v>19.15487945755952</v>
+        <v>12.67828985264331</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14055415262332</v>
+        <v>22.68818944514379</v>
       </c>
       <c r="C3" t="n">
-        <v>32.16696352964674</v>
+        <v>30.63543711102172</v>
       </c>
       <c r="D3" t="n">
-        <v>90.43368977669495</v>
+        <v>98.94544237251478</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.71682435948296</v>
+        <v>51.15298238207581</v>
       </c>
       <c r="C4" t="n">
-        <v>110.0784613386736</v>
+        <v>114.9793458782737</v>
       </c>
       <c r="D4" t="n">
-        <v>166.8598033091964</v>
+        <v>183.298186869105</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.93320976504477</v>
+        <v>49.08738521234053</v>
       </c>
       <c r="C5" t="n">
-        <v>203.5162990903638</v>
+        <v>227.2009624553181</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7738418129166</v>
+        <v>126.4981916922015</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.81139093426016</v>
+        <v>37.47429161880501</v>
       </c>
       <c r="C6" t="n">
-        <v>210.1941469746506</v>
+        <v>189.4242925436051</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>53.05168244208915</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>176.4858395493364</v>
+        <v>139.8352342543944</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>76.18853058807372</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
         <v>31.61718481526852</v>
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.097414006898687</v>
+        <v>3.418445506187394</v>
       </c>
       <c r="C2" t="n">
-        <v>5.142394474844792</v>
+        <v>4.159665022893735</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7900291644782</v>
+        <v>14.63000428868597</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>16.54735755507999</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91890015564179</v>
+        <v>22.55074476654924</v>
       </c>
       <c r="D3" t="n">
-        <v>85.18133955897451</v>
+        <v>87.90078069973816</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.59821281371835</v>
+        <v>47.42626809675492</v>
       </c>
       <c r="C4" t="n">
-        <v>96.65207973539424</v>
+        <v>97.40508022455154</v>
       </c>
       <c r="D4" t="n">
-        <v>172.2711966550048</v>
+        <v>189.0796990994144</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.4989584845982</v>
+        <v>60.62292073724056</v>
       </c>
       <c r="C5" t="n">
-        <v>204.7434837206723</v>
+        <v>222.0222433154162</v>
       </c>
       <c r="D5" t="n">
-        <v>148.3911654969054</v>
+        <v>155.1897683488146</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="C6" t="n">
-        <v>260.2269552261808</v>
+        <v>263.4470876961104</v>
       </c>
       <c r="D6" t="n">
-        <v>73.09700706740053</v>
+        <v>73.62027859376408</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="C7" t="n">
-        <v>230.2041286826091</v>
+        <v>195.4100082963978</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>149.3729132011522</v>
+        <v>119.4983305609218</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>61.4593697812588</v>
+        <v>52.69530802544753</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.116648050356123</v>
+        <v>2.508365384350601</v>
       </c>
       <c r="C2" t="n">
-        <v>2.938370878810703</v>
+        <v>2.924626410951248</v>
       </c>
       <c r="D2" t="n">
-        <v>10.78548027885546</v>
+        <v>10.61072918749953</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.49412219487241</v>
+        <v>14.65749322440488</v>
       </c>
       <c r="C3" t="n">
-        <v>21.82425146540659</v>
+        <v>19.92456965768902</v>
       </c>
       <c r="D3" t="n">
-        <v>79.42338927356695</v>
+        <v>81.60286917699489</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.17780381212246</v>
+        <v>42.55090899746525</v>
       </c>
       <c r="C4" t="n">
-        <v>82.8300538073034</v>
+        <v>82.91939284838985</v>
       </c>
       <c r="D4" t="n">
-        <v>174.8237406860465</v>
+        <v>190.0624285513655</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.64684253504097</v>
+        <v>65.60529033629311</v>
       </c>
       <c r="C5" t="n">
-        <v>201.8227843005381</v>
+        <v>213.92282475538</v>
       </c>
       <c r="D5" t="n">
-        <v>166.0380804807418</v>
+        <v>175.438314748905</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.99884799250906</v>
+        <v>57.11709968537519</v>
       </c>
       <c r="C6" t="n">
-        <v>293.032054763588</v>
+        <v>303.6584919143555</v>
       </c>
       <c r="D6" t="n">
-        <v>86.74231840872694</v>
+        <v>88.07062305257288</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>279.0117157992393</v>
+        <v>251.1045555583194</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>44.0765449298648</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>191.8482276253905</v>
+        <v>155.8819004803085</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.247040568571702</v>
+        <v>3.334996951326415</v>
       </c>
       <c r="C2" t="n">
-        <v>9.072330534944774</v>
+        <v>8.605018627723293</v>
       </c>
       <c r="D2" t="n">
-        <v>15.23279737909351</v>
+        <v>12.98655863177681</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.51942665100457</v>
+        <v>11.72697632722815</v>
       </c>
       <c r="C3" t="n">
-        <v>16.99405276051229</v>
+        <v>15.9288565014045</v>
       </c>
       <c r="D3" t="n">
-        <v>72.04064653763095</v>
+        <v>73.7341613274567</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.9961394291078</v>
+        <v>36.01639627799848</v>
       </c>
       <c r="C4" t="n">
-        <v>70.33535077535424</v>
+        <v>68.34436643114171</v>
       </c>
       <c r="D4" t="n">
-        <v>172.0797558526767</v>
+        <v>185.4295611350248</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.13142499031139</v>
+        <v>64.72171740247099</v>
       </c>
       <c r="C5" t="n">
-        <v>180.8624708148687</v>
+        <v>188.0292290558704</v>
       </c>
       <c r="D5" t="n">
-        <v>183.8568013128214</v>
+        <v>195.6377737637832</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.13597387593413</v>
+        <v>68.34731167425446</v>
       </c>
       <c r="C6" t="n">
-        <v>304.825789934705</v>
+        <v>318.7931145230243</v>
       </c>
       <c r="D6" t="n">
-        <v>108.7599741718702</v>
+        <v>111.8593516741773</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.54217107911827</v>
+        <v>34.19525428662065</v>
       </c>
       <c r="C7" t="n">
-        <v>335.7842220404238</v>
+        <v>326.202364446975</v>
       </c>
       <c r="D7" t="n">
-        <v>53.23919625360028</v>
+        <v>53.83806235319084</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>261.1939767148639</v>
+        <v>220.3876333878452</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>127.0234267139735</v>
+        <v>105.5015535414749</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.503096792930871</v>
+        <v>7.49171673110741</v>
       </c>
       <c r="C2" t="n">
-        <v>6.180101798233672</v>
+        <v>4.068362486398782</v>
       </c>
       <c r="D2" t="n">
-        <v>7.906996010003811</v>
+        <v>5.609706382066275</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.067961575771282</v>
+        <v>2.415099352447153</v>
       </c>
       <c r="C2" t="n">
-        <v>5.297510612115789</v>
+        <v>5.024584750335175</v>
       </c>
       <c r="D2" t="n">
-        <v>11.33231375012093</v>
+        <v>9.661379157492862</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74585051778709</v>
+        <v>15.92394776288327</v>
       </c>
       <c r="C3" t="n">
-        <v>24.64186737659494</v>
+        <v>23.2085157283946</v>
       </c>
       <c r="D3" t="n">
-        <v>77.86731916233578</v>
+        <v>79.2123135171539</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.04865508351838</v>
+        <v>49.18752347817369</v>
       </c>
       <c r="C4" t="n">
-        <v>102.025184920737</v>
+        <v>101.0935063494068</v>
       </c>
       <c r="D4" t="n">
-        <v>176.5722333473101</v>
+        <v>189.9603267901238</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.90113088597411</v>
+        <v>39.68715094417732</v>
       </c>
       <c r="C5" t="n">
-        <v>262.1266370338984</v>
+        <v>273.4167356327367</v>
       </c>
       <c r="D5" t="n">
-        <v>165.4981192434061</v>
+        <v>174.9474408967816</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.95852991671016</v>
+        <v>21.21262264566084</v>
       </c>
       <c r="C6" t="n">
-        <v>277.8974321549192</v>
+        <v>274.1942798145002</v>
       </c>
       <c r="D6" t="n">
-        <v>82.71715282131501</v>
+        <v>84.52847733565039</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>183.672232744423</v>
+        <v>154.9865465740355</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>93.6292785540183</v>
+        <v>77.69060457557134</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.650358948567893</v>
+        <v>7.074473956802516</v>
       </c>
       <c r="C2" t="n">
-        <v>8.546113765468485</v>
+        <v>5.834526606338795</v>
       </c>
       <c r="D2" t="n">
-        <v>19.8695917862512</v>
+        <v>14.47979688993621</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.81319019875262</v>
+        <v>15.90922154731956</v>
       </c>
       <c r="C3" t="n">
-        <v>15.57051858935441</v>
+        <v>10.41143440353742</v>
       </c>
       <c r="D3" t="n">
-        <v>9.778207134298231</v>
+        <v>7.849072895453249</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39846735566139</v>
+        <v>13.39905561391721</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14491733258021</v>
+        <v>70.14799703756657</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576290277136634</v>
+        <v>1.57635948399026</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.833143948007048</v>
+        <v>5.01084028247572</v>
       </c>
       <c r="C2" t="n">
-        <v>7.247261552749954</v>
+        <v>6.631705742187204</v>
       </c>
       <c r="D2" t="n">
-        <v>23.96249796525615</v>
+        <v>23.25073087967721</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3306122966197</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="C3" t="n">
-        <v>26.67899386290707</v>
+        <v>18.36359080793659</v>
       </c>
       <c r="D3" t="n">
-        <v>24.1019061392592</v>
+        <v>18.11324514335365</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.04273923509713</v>
+        <v>18.3910797436555</v>
       </c>
       <c r="C4" t="n">
-        <v>24.27469373520663</v>
+        <v>16.40009539944297</v>
       </c>
       <c r="D4" t="n">
-        <v>20.1906232855399</v>
+        <v>19.18236839327843</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44061361929703</v>
+        <v>15.44369188134776</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14237071818346</v>
+        <v>86.15954418015065</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250655498799376</v>
+        <v>3.251303553967948</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.5553093477052</v>
+        <v>4.846888415866503</v>
       </c>
       <c r="C2" t="n">
-        <v>7.272786993060371</v>
+        <v>5.370159942230052</v>
       </c>
       <c r="D2" t="n">
-        <v>20.21123998732908</v>
+        <v>25.04929267385737</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>18.97718312309085</v>
       </c>
       <c r="C3" t="n">
-        <v>27.60183670489907</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="D3" t="n">
-        <v>37.67947688899258</v>
+        <v>32.51057522613313</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.21837426316607</v>
+        <v>31.01340997715674</v>
       </c>
       <c r="C4" t="n">
-        <v>49.30238795957057</v>
+        <v>33.80844569114741</v>
       </c>
       <c r="D4" t="n">
-        <v>27.72062817711294</v>
+        <v>23.95562573132642</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.8671863224862</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C5" t="n">
-        <v>27.85709110800325</v>
+        <v>19.53677931451153</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>29.35425635697964</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73185862203844</v>
+        <v>16.73899840606538</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0643375944345</v>
+        <v>102.1078902769988</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182964655509609</v>
+        <v>5.021699521819613</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.404922022506191</v>
+        <v>5.78053048260522</v>
       </c>
       <c r="C2" t="n">
-        <v>8.647233779005905</v>
+        <v>6.064255569132548</v>
       </c>
       <c r="D2" t="n">
-        <v>34.87953243648068</v>
+        <v>33.03777374331366</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78297700409922</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94544840138546</v>
+        <v>21.68680678681204</v>
       </c>
       <c r="D3" t="n">
-        <v>44.6597030661874</v>
+        <v>44.31609136970102</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.42181702212341</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="C4" t="n">
-        <v>60.34214089382595</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="D4" t="n">
-        <v>39.67929696254333</v>
+        <v>34.26790361673491</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.9798095710341</v>
+        <v>31.1214022246239</v>
       </c>
       <c r="C5" t="n">
-        <v>61.97282383057992</v>
+        <v>43.12326790904115</v>
       </c>
       <c r="D5" t="n">
-        <v>32.7658296292373</v>
+        <v>31.04777114680538</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.43776166510284</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="C6" t="n">
-        <v>28.6591789823729</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05458821985563</v>
+        <v>18.06744533965152</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7846945771534</v>
+        <v>117.8685719777266</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018196073285211</v>
+        <v>6.882836319867245</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.119634351197869</v>
+        <v>8.181885367192917</v>
       </c>
       <c r="C2" t="n">
-        <v>7.527059648460295</v>
+        <v>5.809982913732624</v>
       </c>
       <c r="D2" t="n">
-        <v>35.90644053512284</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>16.79770321966292</v>
       </c>
       <c r="C3" t="n">
-        <v>29.18735924725767</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="D3" t="n">
-        <v>57.60404654668159</v>
+        <v>56.03815895840794</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.3302524437212</v>
+        <v>24.75967710110456</v>
       </c>
       <c r="C4" t="n">
-        <v>54.36918786118836</v>
+        <v>42.21907827342983</v>
       </c>
       <c r="D4" t="n">
-        <v>45.72882631611218</v>
+        <v>41.60646770597982</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.89926520155685</v>
+        <v>25.37817815478006</v>
       </c>
       <c r="C5" t="n">
-        <v>65.75255249193013</v>
+        <v>49.50462798664542</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56318869153496</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.72581465307466</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>43.35103337642641</v>
+        <v>31.396291581813</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>20.24167416616073</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053735774941468</v>
+        <v>7.062236695478788</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12877289007626</v>
+        <v>66.20846902011364</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408584859338418</v>
+        <v>5.296677521609091</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.62050560681299</v>
+        <v>6.528622233241289</v>
       </c>
       <c r="C2" t="n">
-        <v>3.878885179479147</v>
+        <v>10.56949578392116</v>
       </c>
       <c r="D2" t="n">
-        <v>39.73231133857266</v>
+        <v>36.67711248295659</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.97642235956485</v>
+        <v>24.06754496961056</v>
       </c>
       <c r="C3" t="n">
-        <v>29.31007771028852</v>
+        <v>22.46238747316702</v>
       </c>
       <c r="D3" t="n">
-        <v>73.84706231344508</v>
+        <v>76.28179661997716</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.12001956629214</v>
+        <v>30.0562059655161</v>
       </c>
       <c r="C4" t="n">
-        <v>65.52380527684062</v>
+        <v>49.00884539600077</v>
       </c>
       <c r="D4" t="n">
-        <v>65.30683903420207</v>
+        <v>60.91646330081034</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.89421759431538</v>
+        <v>32.39767424014475</v>
       </c>
       <c r="C5" t="n">
-        <v>87.10556505929826</v>
+        <v>67.32334881872504</v>
       </c>
       <c r="D5" t="n">
-        <v>41.11068511533519</v>
+        <v>38.80357801035519</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.70822530985623</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="C6" t="n">
-        <v>79.33601372788901</v>
+        <v>59.65295400544471</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>33.2881194078966</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.73777555197486</v>
+        <v>13.29482741091031</v>
       </c>
       <c r="C7" t="n">
-        <v>44.91495746929157</v>
+        <v>33.83593462686632</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>23.78283813537898</v>
+        <v>21.36283004441059</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27236205945343</v>
+        <v>7.285230889687476</v>
       </c>
       <c r="C21" t="n">
-        <v>75.45075636682934</v>
+        <v>75.58427048050757</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454271544590072</v>
+        <v>6.374577028476542</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.744786654624835</v>
+        <v>5.506622873120359</v>
       </c>
       <c r="C2" t="n">
-        <v>5.64504929941916</v>
+        <v>9.040914608408876</v>
       </c>
       <c r="D2" t="n">
-        <v>32.56751659297944</v>
+        <v>41.6123581922053</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.52343575727957</v>
+        <v>23.25269437508571</v>
       </c>
       <c r="C3" t="n">
-        <v>20.81305133003238</v>
+        <v>33.78193850313274</v>
       </c>
       <c r="D3" t="n">
-        <v>89.20650514638643</v>
+        <v>87.92532439234435</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.21609197258809</v>
+        <v>39.43680527959437</v>
       </c>
       <c r="C4" t="n">
-        <v>70.10562181256049</v>
+        <v>53.29711936815084</v>
       </c>
       <c r="D4" t="n">
-        <v>85.80376760346698</v>
+        <v>85.44641143912114</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>39.785325714602</v>
       </c>
       <c r="C5" t="n">
-        <v>106.2005579068987</v>
+        <v>80.65057390387548</v>
       </c>
       <c r="D5" t="n">
-        <v>55.24785205648926</v>
+        <v>51.51721078035138</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.8453511932813</v>
+        <v>36.10573531908495</v>
       </c>
       <c r="C6" t="n">
-        <v>111.3360801478138</v>
+        <v>85.1725038296363</v>
       </c>
       <c r="D6" t="n">
-        <v>39.36611944488861</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>23.47555110394973</v>
       </c>
       <c r="C7" t="n">
-        <v>81.68533598415159</v>
+        <v>62.8809404570082</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>43.14290286312608</v>
+        <v>34.46425315758427</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.476552695977202</v>
+        <v>7.495117897509415</v>
       </c>
       <c r="C21" t="n">
-        <v>84.11121782974352</v>
+        <v>85.25696608416959</v>
       </c>
       <c r="D21" t="n">
-        <v>6.541983608980051</v>
+        <v>7.495117897509415</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_55_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_55_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622413629</v>
+        <v>10.84497642141702</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890715653115</v>
+        <v>37.78907225273171</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.201700247727102</v>
+        <v>0.7824529202847079</v>
       </c>
       <c r="C2" t="n">
-        <v>10.18465068385641</v>
+        <v>2.638937829015426</v>
       </c>
       <c r="D2" t="n">
-        <v>38.17231423652448</v>
+        <v>19.58488495201962</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.80323385298991</v>
+        <v>6.307728999785756</v>
       </c>
       <c r="C3" t="n">
-        <v>34.44461820349934</v>
+        <v>31.63191103083223</v>
       </c>
       <c r="D3" t="n">
-        <v>99.17124434449156</v>
+        <v>82.46680715673207</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.98934931063608</v>
+        <v>10.56753228851267</v>
       </c>
       <c r="C4" t="n">
-        <v>70.08009637225007</v>
+        <v>78.52901711499813</v>
       </c>
       <c r="D4" t="n">
-        <v>106.7601540983194</v>
+        <v>91.90434783765667</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.75006491270713</v>
+        <v>10.50470043544087</v>
       </c>
       <c r="C5" t="n">
-        <v>89.09360416039806</v>
+        <v>79.81608835526569</v>
       </c>
       <c r="D5" t="n">
-        <v>69.43410638285567</v>
+        <v>52.37624002156735</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.00135126726531</v>
+        <v>8.010079518949729</v>
       </c>
       <c r="C6" t="n">
-        <v>107.3109145604019</v>
+        <v>55.34602682691394</v>
       </c>
       <c r="D6" t="n">
-        <v>44.92084795551706</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>92.88413204649498</v>
+        <v>36.11162580531042</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>29.2845522699781</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.85799074024948</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>59.41537106101696</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.689536051041334</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.19681662525633</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.650728057421501</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.637015391335938</v>
+        <v>1.107411410390402</v>
       </c>
       <c r="C2" t="n">
-        <v>14.00757624419349</v>
+        <v>5.683337459884785</v>
       </c>
       <c r="D2" t="n">
-        <v>35.48134377918397</v>
+        <v>23.2841103016216</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.62651926622549</v>
+        <v>4.3245986372072</v>
       </c>
       <c r="C3" t="n">
-        <v>36.82535638629786</v>
+        <v>18.67775007329557</v>
       </c>
       <c r="D3" t="n">
-        <v>104.9733732765902</v>
+        <v>79.00123776074084</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.35572113076939</v>
+        <v>11.65236350170539</v>
       </c>
       <c r="C4" t="n">
-        <v>77.09959245761476</v>
+        <v>79.74147552974293</v>
       </c>
       <c r="D4" t="n">
-        <v>128.1632357986041</v>
+        <v>112.6310053697153</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.54237636776331</v>
+        <v>13.49903093339365</v>
       </c>
       <c r="C5" t="n">
-        <v>108.2867717784232</v>
+        <v>117.196132194463</v>
       </c>
       <c r="D5" t="n">
-        <v>87.52280783360315</v>
+        <v>73.45927197026759</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>122.3247822014483</v>
+        <v>93.70585487494957</v>
       </c>
       <c r="D6" t="n">
-        <v>54.90325861229863</v>
+        <v>40.53341746523807</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.69915290080652</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>121.3302717770463</v>
+        <v>59.04819741962866</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.20284622634736</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>89.54029936583034</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.7578114166873</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.867954333563616</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.283406336327</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.834942916954519</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.690831588620265</v>
+        <v>0.56941366846315</v>
       </c>
       <c r="C2" t="n">
-        <v>9.619164006210248</v>
+        <v>2.32085157283946</v>
       </c>
       <c r="D2" t="n">
-        <v>33.00243082596078</v>
+        <v>15.70207278172349</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.37403017978481</v>
+        <v>4.540583132141498</v>
       </c>
       <c r="C3" t="n">
-        <v>44.65479432766617</v>
+        <v>21.76534660315179</v>
       </c>
       <c r="D3" t="n">
-        <v>106.9466861621263</v>
+        <v>81.63723034664352</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.90077103307561</v>
+        <v>12.74995743505333</v>
       </c>
       <c r="C4" t="n">
-        <v>83.54476613599506</v>
+        <v>73.15591192965532</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8741443096658</v>
+        <v>125.2916237636822</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.16226007977055</v>
+        <v>13.84264262988003</v>
       </c>
       <c r="C5" t="n">
-        <v>121.4912784005428</v>
+        <v>142.0343491119073</v>
       </c>
       <c r="D5" t="n">
-        <v>107.7468105410875</v>
+        <v>85.16661334341082</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.35610634586367</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>142.3298551708856</v>
+        <v>125.907179574245</v>
       </c>
       <c r="D6" t="n">
-        <v>65.52969576306612</v>
+        <v>40.73467574460867</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.4007837141735</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>145.6442354204228</v>
+        <v>59.76683673913732</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.79804737702819</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>118.9976392317559</v>
+        <v>40.63944621729671</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.19374845510188</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>76.76874348128355</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.53926689373453</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.029580542055871</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4067324532682</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04067324532682</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.754244278768809</v>
+        <v>0.5429064804484861</v>
       </c>
       <c r="C2" t="n">
-        <v>6.617961274327748</v>
+        <v>6.120215188274616</v>
       </c>
       <c r="D2" t="n">
-        <v>27.42806736124739</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.85079971115026</v>
+        <v>3.195588777323368</v>
       </c>
       <c r="C3" t="n">
-        <v>61.51631114810514</v>
+        <v>14.27461161974862</v>
       </c>
       <c r="D3" t="n">
-        <v>114.5306871774329</v>
+        <v>75.41294990171875</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.45261105385356</v>
+        <v>10.92488845285851</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3517470533527</v>
+        <v>63.26480380936871</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6429505730823</v>
+        <v>137.339631590199</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.68652904937156</v>
+        <v>16.61607989437727</v>
       </c>
       <c r="C5" t="n">
-        <v>85.04389488037997</v>
+        <v>141.1016887928728</v>
       </c>
       <c r="D5" t="n">
-        <v>68.10874698212248</v>
+        <v>110.2993545721292</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.52333794628834</v>
+        <v>13.92707293244525</v>
       </c>
       <c r="C6" t="n">
-        <v>95.91969594802613</v>
+        <v>177.1877891578729</v>
       </c>
       <c r="D6" t="n">
-        <v>30.91327171132357</v>
+        <v>55.34602682691394</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>83.66159411280043</v>
+        <v>119.6534466981928</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>56.57812019574367</v>
+        <v>59.74916528046088</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.271003424101125</v>
+        <v>0.2896155727528091</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1857713002809</v>
+        <v>3.30259927708627</v>
       </c>
       <c r="D2" t="n">
-        <v>19.38657191576177</v>
+        <v>15.22396164975529</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.1039106923967</v>
+        <v>2.626175108860218</v>
       </c>
       <c r="C3" t="n">
-        <v>44.20809912223388</v>
+        <v>19.58095796120263</v>
       </c>
       <c r="D3" t="n">
-        <v>112.1057703479433</v>
+        <v>75.22641783791185</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.99461790205581</v>
+        <v>9.227446672215772</v>
       </c>
       <c r="C4" t="n">
-        <v>132.9109676963417</v>
+        <v>51.21679598285185</v>
       </c>
       <c r="D4" t="n">
-        <v>153.6631506687108</v>
+        <v>143.5040254251647</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.46625771072178</v>
+        <v>17.62237129123025</v>
       </c>
       <c r="C5" t="n">
-        <v>135.5302705712722</v>
+        <v>135.1866588747858</v>
       </c>
       <c r="D5" t="n">
-        <v>90.66440048719295</v>
+        <v>129.7134154236099</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.76234460677682</v>
+        <v>16.98619877887832</v>
       </c>
       <c r="C6" t="n">
-        <v>115.4820007028481</v>
+        <v>206.4507429783575</v>
       </c>
       <c r="D6" t="n">
-        <v>39.16486116551801</v>
+        <v>68.99133816824036</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>106.5981657271187</v>
+        <v>171.5152509227348</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>74.10231671654924</v>
+        <v>88.03822537833271</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>49.47812079863073</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.719261214314417</v>
+        <v>0.5517422097867074</v>
       </c>
       <c r="C2" t="n">
-        <v>7.810784734987623</v>
+        <v>10.08254892261474</v>
       </c>
       <c r="D2" t="n">
-        <v>18.07495698288803</v>
+        <v>23.79461910782994</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.4834050855837</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C3" t="n">
-        <v>27.71473769088746</v>
+        <v>15.88958659323463</v>
       </c>
       <c r="D3" t="n">
-        <v>102.5042778004095</v>
+        <v>70.89691046218341</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.49458952542469</v>
+        <v>7.159886007071989</v>
       </c>
       <c r="C4" t="n">
-        <v>121.5138585977405</v>
+        <v>49.99157484795184</v>
       </c>
       <c r="D4" t="n">
-        <v>171.4799080053819</v>
+        <v>146.2607729786898</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.34478303730243</v>
+        <v>16.29701189049706</v>
       </c>
       <c r="C5" t="n">
-        <v>188.0292290558704</v>
+        <v>116.042578641973</v>
       </c>
       <c r="D5" t="n">
-        <v>119.355977143806</v>
+        <v>149.6183501272139</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.28311285838414</v>
+        <v>20.20633124880786</v>
       </c>
       <c r="C6" t="n">
-        <v>162.6569413873158</v>
+        <v>211.2809416832519</v>
       </c>
       <c r="D6" t="n">
-        <v>54.37998708593508</v>
+        <v>90.12345750215297</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.38058361854505</v>
+        <v>13.35471402086936</v>
       </c>
       <c r="C7" t="n">
-        <v>135.04430545767</v>
+        <v>232.8990261307666</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>50.84373185523806</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>103.9768993567797</v>
+        <v>150.9584357435108</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>42.80910864368217</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>61.90311974357836</v>
+        <v>75.65936857548466</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.852958828541231</v>
+        <v>0.3661918936840602</v>
       </c>
       <c r="C2" t="n">
-        <v>3.704134088123216</v>
+        <v>5.162029428929729</v>
       </c>
       <c r="D2" t="n">
-        <v>12.67828985264331</v>
+        <v>17.13247918681109</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.68818944514379</v>
+        <v>2.650718801466388</v>
       </c>
       <c r="C3" t="n">
-        <v>30.63543711102172</v>
+        <v>27.02260555939346</v>
       </c>
       <c r="D3" t="n">
-        <v>98.94544237251478</v>
+        <v>79.59519512181015</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.15298238207581</v>
+        <v>11.34605821798039</v>
       </c>
       <c r="C4" t="n">
-        <v>114.9793458782737</v>
+        <v>70.18219813349174</v>
       </c>
       <c r="D4" t="n">
-        <v>183.298186869105</v>
+        <v>151.5828272834117</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.08738521234053</v>
+        <v>12.56637061435918</v>
       </c>
       <c r="C5" t="n">
-        <v>227.2009624553181</v>
+        <v>175.8555575232099</v>
       </c>
       <c r="D5" t="n">
-        <v>126.4981916922015</v>
+        <v>137.8619213688584</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.47429161880501</v>
+        <v>8.291841110068562</v>
       </c>
       <c r="C6" t="n">
-        <v>189.4242925436051</v>
+        <v>207.2155244399658</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>74.38506005537235</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>139.8352342543944</v>
+        <v>106.1190728474462</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>76.18853058807372</v>
+        <v>55.7436346471339</v>
       </c>
       <c r="D8" t="n">
         <v>31.46010518258904</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.418445506187394</v>
+        <v>0.2621266370338984</v>
       </c>
       <c r="C2" t="n">
-        <v>4.159665022893735</v>
+        <v>2.64090132442392</v>
       </c>
       <c r="D2" t="n">
-        <v>14.63000428868597</v>
+        <v>13.13872952593506</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54735755507999</v>
+        <v>1.953677931451153</v>
       </c>
       <c r="C3" t="n">
-        <v>22.55074476654924</v>
+        <v>23.47849634706247</v>
       </c>
       <c r="D3" t="n">
-        <v>87.90078069973816</v>
+        <v>74.76008767839461</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.42626809675492</v>
+        <v>7.734208414056372</v>
       </c>
       <c r="C4" t="n">
-        <v>97.40508022455154</v>
+        <v>66.03431408304895</v>
       </c>
       <c r="D4" t="n">
-        <v>189.0796990994144</v>
+        <v>149.9747245438555</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.62292073724056</v>
+        <v>11.75642875835556</v>
       </c>
       <c r="C5" t="n">
-        <v>222.0222433154162</v>
+        <v>138.7209506100743</v>
       </c>
       <c r="D5" t="n">
-        <v>155.1897683488146</v>
+        <v>142.9179220457295</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>7.84907289545325</v>
       </c>
       <c r="C6" t="n">
-        <v>263.4470876961104</v>
+        <v>199.4067032003867</v>
       </c>
       <c r="D6" t="n">
-        <v>73.62027859376408</v>
+        <v>81.59010645683969</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>195.4100082963978</v>
+        <v>141.0928530635346</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>119.4983305609218</v>
+        <v>60.4167537193487</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>52.69530802544753</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.508365384350601</v>
+        <v>0.3269219855141878</v>
       </c>
       <c r="C2" t="n">
-        <v>2.924626410951248</v>
+        <v>6.83001877844506</v>
       </c>
       <c r="D2" t="n">
-        <v>10.61072918749953</v>
+        <v>14.19410830800038</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65749322440488</v>
+        <v>1.374446785945534</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92456965768902</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="D3" t="n">
-        <v>81.60286917699489</v>
+        <v>67.92221491831558</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.55090899746525</v>
+        <v>5.692173189223007</v>
       </c>
       <c r="C4" t="n">
-        <v>82.91939284838985</v>
+        <v>61.87366731245098</v>
       </c>
       <c r="D4" t="n">
-        <v>190.0624285513655</v>
+        <v>153.9311677919701</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.60529033629311</v>
+        <v>11.87914722138641</v>
       </c>
       <c r="C5" t="n">
-        <v>213.92282475538</v>
+        <v>129.5170658827605</v>
       </c>
       <c r="D5" t="n">
-        <v>175.438314748905</v>
+        <v>165.1054201617074</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.11709968537519</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>303.6584919143555</v>
+        <v>213.6557893798249</v>
       </c>
       <c r="D6" t="n">
-        <v>88.07062305257288</v>
+        <v>106.8278946899124</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>251.1045555583194</v>
+        <v>220.1431782094878</v>
       </c>
       <c r="D7" t="n">
-        <v>44.0765449298648</v>
+        <v>51.3228247349105</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>155.8819004803085</v>
+        <v>125.0059351817464</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>52.80624551602742</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.334996951326415</v>
+        <v>0.2444551783574558</v>
       </c>
       <c r="C2" t="n">
-        <v>8.605018627723293</v>
+        <v>6.345035412547136</v>
       </c>
       <c r="D2" t="n">
-        <v>12.98655863177681</v>
+        <v>19.00467205880975</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.72697632722815</v>
+        <v>1.241910845872215</v>
       </c>
       <c r="C3" t="n">
-        <v>15.9288565014045</v>
+        <v>21.68189804829081</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7341613274567</v>
+        <v>63.68597357449059</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.01639627799848</v>
+        <v>4.09683316982194</v>
       </c>
       <c r="C4" t="n">
-        <v>68.34436643114171</v>
+        <v>49.65974412391641</v>
       </c>
       <c r="D4" t="n">
-        <v>185.4295611350248</v>
+        <v>151.6849290446534</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.72171740247099</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C5" t="n">
-        <v>188.0292290558704</v>
+        <v>121.5649094783613</v>
       </c>
       <c r="D5" t="n">
-        <v>195.6377737637832</v>
+        <v>182.7032477603314</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.34731167425446</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>318.7931145230243</v>
+        <v>210.7979218127624</v>
       </c>
       <c r="D6" t="n">
-        <v>111.8593516741773</v>
+        <v>132.1059345788593</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.19525428662065</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>326.202364446975</v>
+        <v>266.0163214381242</v>
       </c>
       <c r="D7" t="n">
-        <v>53.83806235319084</v>
+        <v>67.13288976410114</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>220.3876333878452</v>
+        <v>206.8689675003666</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>105.5015535414749</v>
+        <v>101.6187413711788</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.49171673110741</v>
+        <v>2.1392282475538</v>
       </c>
       <c r="C2" t="n">
-        <v>4.068362486398782</v>
+        <v>7.050912011900593</v>
       </c>
       <c r="D2" t="n">
-        <v>5.609706382066275</v>
+        <v>15.38889526406875</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.415099352447153</v>
+        <v>0.2415099352447153</v>
       </c>
       <c r="C2" t="n">
-        <v>5.024584750335175</v>
+        <v>7.476990515543707</v>
       </c>
       <c r="D2" t="n">
-        <v>9.661379157492862</v>
+        <v>29.55158764553324</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.92394776288327</v>
+        <v>1.035743827980385</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2085157283946</v>
+        <v>23.05143609571511</v>
       </c>
       <c r="D3" t="n">
-        <v>79.2123135171539</v>
+        <v>63.66633862040566</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.18752347817369</v>
+        <v>3.22896819926776</v>
       </c>
       <c r="C4" t="n">
-        <v>101.0935063494068</v>
+        <v>51.77835566968103</v>
       </c>
       <c r="D4" t="n">
-        <v>189.9603267901238</v>
+        <v>149.3365885360951</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.68715094417732</v>
+        <v>8.614836104765763</v>
       </c>
       <c r="C5" t="n">
-        <v>273.4167356327367</v>
+        <v>107.2559366889641</v>
       </c>
       <c r="D5" t="n">
-        <v>174.9474408967816</v>
+        <v>193.8706278961389</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.21262264566084</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>274.1942798145002</v>
+        <v>201.7815508969597</v>
       </c>
       <c r="D6" t="n">
-        <v>84.52847733565039</v>
+        <v>153.1575506010237</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>12.99539436111503</v>
       </c>
       <c r="C7" t="n">
-        <v>154.9865465740355</v>
+        <v>286.4376554341621</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>85.4581924115721</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>77.69060457557134</v>
+        <v>272.1257374016521</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>44.06083696659685</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>171.1765479647696</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>76.87084524252526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.074473956802516</v>
+        <v>2.980586030093316</v>
       </c>
       <c r="C2" t="n">
-        <v>5.834526606338795</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="D2" t="n">
-        <v>14.47979688993621</v>
+        <v>15.2828665120101</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90922154731956</v>
+        <v>3.54901795085222</v>
       </c>
       <c r="C3" t="n">
-        <v>10.41143440353742</v>
+        <v>13.92118244621977</v>
       </c>
       <c r="D3" t="n">
-        <v>7.849072895453249</v>
+        <v>13.48921345635117</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39905561391721</v>
+        <v>11.67791239613626</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14799703756657</v>
+        <v>59.94661696683281</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57635948399026</v>
+        <v>0.7785274930757508</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.01084028247572</v>
+        <v>1.993929587325272</v>
       </c>
       <c r="C2" t="n">
-        <v>6.631705742187204</v>
+        <v>3.385066084243002</v>
       </c>
       <c r="D2" t="n">
-        <v>23.25073087967721</v>
+        <v>24.2697849966854</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.07321447165778</v>
+        <v>7.824529202847079</v>
       </c>
       <c r="C3" t="n">
-        <v>18.36359080793659</v>
+        <v>18.55994034878595</v>
       </c>
       <c r="D3" t="n">
-        <v>18.11324514335365</v>
+        <v>23.54721868635975</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.3910797436555</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C4" t="n">
-        <v>16.40009539944297</v>
+        <v>23.18986252201391</v>
       </c>
       <c r="D4" t="n">
-        <v>19.18236839327843</v>
+        <v>21.40308170028471</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44369188134776</v>
+        <v>13.63066858904947</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15954418015065</v>
+        <v>73.76597118779712</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251303553967948</v>
+        <v>1.603608069299937</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.846888415866503</v>
+        <v>1.073050240741764</v>
       </c>
       <c r="C2" t="n">
-        <v>5.370159942230052</v>
+        <v>3.659955441432109</v>
       </c>
       <c r="D2" t="n">
-        <v>25.04929267385737</v>
+        <v>29.29829673783756</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.97718312309085</v>
+        <v>7.343472827766142</v>
       </c>
       <c r="C3" t="n">
-        <v>22.87472150895069</v>
+        <v>15.11891464540088</v>
       </c>
       <c r="D3" t="n">
-        <v>32.51057522613313</v>
+        <v>38.2439818189345</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.01340997715674</v>
+        <v>10.93765117301371</v>
       </c>
       <c r="C4" t="n">
-        <v>33.80844569114741</v>
+        <v>37.86699070050372</v>
       </c>
       <c r="D4" t="n">
-        <v>23.95562573132642</v>
+        <v>28.5629677073567</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.97794388661684</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C5" t="n">
-        <v>19.53677931451153</v>
+        <v>28.10252803406495</v>
       </c>
       <c r="D5" t="n">
-        <v>29.35425635697964</v>
+        <v>27.88163480060942</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73899840606538</v>
+        <v>14.84477309245539</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1078902769988</v>
+        <v>87.41921932223727</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021699521819613</v>
+        <v>2.474128848742564</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.78053048260522</v>
+        <v>0.828595062384308</v>
       </c>
       <c r="C2" t="n">
-        <v>6.064255569132548</v>
+        <v>4.905793278121311</v>
       </c>
       <c r="D2" t="n">
-        <v>33.03777374331366</v>
+        <v>31.80469862677967</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>5.271985171805373</v>
       </c>
       <c r="C3" t="n">
-        <v>21.68680678681204</v>
+        <v>14.5887708851076</v>
       </c>
       <c r="D3" t="n">
-        <v>44.31609136970102</v>
+        <v>52.80820901143593</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>12.96692367769187</v>
       </c>
       <c r="C4" t="n">
-        <v>46.57116584635595</v>
+        <v>37.90527886096935</v>
       </c>
       <c r="D4" t="n">
-        <v>34.26790361673491</v>
+        <v>41.01938257884023</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.1214022246239</v>
+        <v>11.02011798017045</v>
       </c>
       <c r="C5" t="n">
-        <v>43.12326790904115</v>
+        <v>52.40078371417351</v>
       </c>
       <c r="D5" t="n">
-        <v>31.04777114680538</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.8063179648229</v>
+        <v>5.796238445873169</v>
       </c>
       <c r="C6" t="n">
-        <v>22.13841073076558</v>
+        <v>29.46421209985528</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>34.17365583712723</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06744533965152</v>
+        <v>16.094146374475</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8685719777266</v>
+        <v>101.6472402598421</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882836319867245</v>
+        <v>3.388241341994737</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.181885367192917</v>
+        <v>1.810342766631118</v>
       </c>
       <c r="C2" t="n">
-        <v>5.809982913732624</v>
+        <v>6.017131679328701</v>
       </c>
       <c r="D2" t="n">
-        <v>40.22220344299182</v>
+        <v>24.30512791403828</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.79770321966292</v>
+        <v>3.922082078466007</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3775562599743</v>
+        <v>17.40147805777471</v>
       </c>
       <c r="D3" t="n">
-        <v>56.03815895840794</v>
+        <v>65.23222620867931</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.75967710110456</v>
+        <v>11.56302446061893</v>
       </c>
       <c r="C4" t="n">
-        <v>42.21907827342983</v>
+        <v>36.75663404700058</v>
       </c>
       <c r="D4" t="n">
-        <v>41.60646770597982</v>
+        <v>56.93449461238528</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.37817815478006</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="C5" t="n">
-        <v>49.50462798664542</v>
+        <v>62.3164355270663</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>39.73623832938966</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.49688751153591</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>31.396291581813</v>
+        <v>58.40515267334701</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>17.00779722837174</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062236695478788</v>
+        <v>17.37374843784771</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20846902011364</v>
+        <v>115.5354271116873</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296677521609091</v>
+        <v>4.343437109461928</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.528622233241289</v>
+        <v>1.762237129123025</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56949578392116</v>
+        <v>11.45699570856028</v>
       </c>
       <c r="D2" t="n">
-        <v>36.67711248295659</v>
+        <v>35.71696322820321</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.06754496961056</v>
+        <v>5.134540493210818</v>
       </c>
       <c r="C3" t="n">
-        <v>22.46238747316702</v>
+        <v>20.75414646777757</v>
       </c>
       <c r="D3" t="n">
-        <v>76.28179661997716</v>
+        <v>69.1935781953152</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.0562059655161</v>
+        <v>9.508226515630358</v>
       </c>
       <c r="C4" t="n">
-        <v>49.00884539600077</v>
+        <v>40.47058561216627</v>
       </c>
       <c r="D4" t="n">
-        <v>60.91646330081034</v>
+        <v>75.74674412116265</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.39767424014475</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>67.32334881872504</v>
+        <v>65.26167863980673</v>
       </c>
       <c r="D5" t="n">
-        <v>38.80357801035519</v>
+        <v>50.56000676871075</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.64659618866693</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>59.65295400544471</v>
+        <v>79.21525876026665</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2881194078966</v>
+        <v>40.37241084174159</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.29482741091031</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>33.83593462686632</v>
+        <v>57.43125895073415</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>21.36283004441059</v>
+        <v>33.46287049925253</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.65056423721292</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285230889687476</v>
+        <v>18.67956951672909</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58427048050757</v>
+        <v>128.9779799964627</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374577028476542</v>
+        <v>5.337019861922595</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.506622873120359</v>
+        <v>1.558033606639688</v>
       </c>
       <c r="C2" t="n">
-        <v>9.040914608408876</v>
+        <v>6.874197425136166</v>
       </c>
       <c r="D2" t="n">
-        <v>41.6123581922053</v>
+        <v>27.84825537866502</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.25269437508571</v>
+        <v>6.744606728175587</v>
       </c>
       <c r="C3" t="n">
-        <v>33.78193850313274</v>
+        <v>36.30993884156828</v>
       </c>
       <c r="D3" t="n">
-        <v>87.92532439234435</v>
+        <v>77.87713663937824</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.43680527959437</v>
+        <v>7.951174656694918</v>
       </c>
       <c r="C4" t="n">
-        <v>53.29711936815084</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="D4" t="n">
-        <v>85.44641143912114</v>
+        <v>69.76102836836986</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.785325714602</v>
+        <v>8.713010875190443</v>
       </c>
       <c r="C5" t="n">
-        <v>80.65057390387548</v>
+        <v>47.32023934469627</v>
       </c>
       <c r="D5" t="n">
-        <v>51.51721078035138</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>6.078000036992004</v>
       </c>
       <c r="C6" t="n">
-        <v>85.1725038296363</v>
+        <v>37.79630486579796</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>26.1635763181775</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>5.150248456478767</v>
+      </c>
+      <c r="C7" t="n">
         <v>23.47555110394973</v>
       </c>
-      <c r="C7" t="n">
-        <v>62.8809404570082</v>
-      </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>34.46425315758427</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495117897509415</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.25696608416959</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495117897509415</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
